--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488172_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488172_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0582</v>
+        <v>3.3497</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1088</v>
+        <v>4.7943</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0506</v>
+        <v>-1.4445</v>
       </c>
       <c r="G2" t="n">
         <v>3.5455</v>
@@ -610,13 +610,13 @@
         <v>1.8529</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6171</v>
+        <v>-0.3255</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0943</v>
+        <v>-0.4088</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4772</v>
+        <v>0.0833</v>
       </c>
       <c r="V2" t="n">
         <v>0.315</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7561</v>
+        <v>1.5888</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2258</v>
+        <v>2.0093</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4697</v>
+        <v>-0.4204</v>
       </c>
       <c r="G3" t="n">
         <v>-0.9374</v>
@@ -688,13 +688,13 @@
         <v>1.8529</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1212</v>
+        <v>-0.2885</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.2037</v>
+        <v>-0.4203</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0825</v>
+        <v>0.1318</v>
       </c>
       <c r="V3" t="n">
         <v>1.8883</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6708</v>
+        <v>0.1089</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1723</v>
+        <v>0.3888</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5014999999999999</v>
+        <v>-0.2799</v>
       </c>
       <c r="G4" t="n">
         <v>1.1746</v>
@@ -766,13 +766,13 @@
         <v>1.8529</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5904</v>
+        <v>0.0286</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0831</v>
+        <v>0.2997</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4927</v>
+        <v>-0.2711</v>
       </c>
       <c r="V4" t="n">
         <v>0.9439</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1469</v>
+        <v>-0.3159</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0577</v>
+        <v>0.1763</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9108000000000001</v>
+        <v>-0.4922</v>
       </c>
       <c r="G5" t="n">
         <v>0.0664</v>
@@ -844,13 +844,13 @@
         <v>0.9264</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7093</v>
+        <v>0.2465</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0831</v>
+        <v>0.2018</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3738</v>
+        <v>0.0448</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6289</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. ARANDA SUAREZ</t>
+          <t>A. ELIAS GALLEGOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0533</v>
+        <v>-0.379</v>
       </c>
       <c r="E6" t="n">
-        <v>2.535</v>
+        <v>1.5741</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.4817</v>
+        <v>-1.9531</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2017</v>
+        <v>1.5107</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4796</v>
+        <v>1.1896</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2778</v>
+        <v>0.3211</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3098</v>
+        <v>2.1227</v>
       </c>
       <c r="K6" t="n">
-        <v>4.144</v>
+        <v>2.0398</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1659</v>
+        <v>0.0829</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.1081</v>
+        <v>-0.612</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6644</v>
+        <v>-0.8501</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.4437</v>
+        <v>0.2381</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.7793</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.7057</v>
+        <v>-0.9264</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9264</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5753</v>
+        <v>0.0547</v>
       </c>
       <c r="T6" t="n">
-        <v>1.302</v>
+        <v>0.0634</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2733</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9444</v>
+        <v>-1.5738</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6289</v>
+        <v>0.3144</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.5733</v>
+        <v>-1.8883</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ELIAS GALLEGOS</t>
+          <t>C. ARANDA SUAREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6722</v>
+        <v>-0.903</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1824</v>
+        <v>1.8495</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8546</v>
+        <v>-2.7525</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5107</v>
+        <v>2.2017</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1896</v>
+        <v>3.4796</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3211</v>
+        <v>-1.2778</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1227</v>
+        <v>4.3098</v>
       </c>
       <c r="K7" t="n">
-        <v>2.0398</v>
+        <v>4.144</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0829</v>
+        <v>0.1659</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.612</v>
+        <v>-2.1081</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8501</v>
+        <v>-0.6644</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2381</v>
+        <v>-1.4437</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3706</v>
+        <v>-2.7793</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9264</v>
+        <v>-3.7057</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.9264</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2385</v>
+        <v>0.619</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3283</v>
+        <v>0.6165</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0898</v>
+        <v>0.0025</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.5738</v>
+        <v>-0.9444</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3144</v>
+        <v>0.6289</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.8883</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. VARO BARBANCHO</t>
+          <t>R. SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.196</v>
+        <v>-1.2155</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6256</v>
+        <v>0.1877</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4297</v>
+        <v>-1.4031</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5253</v>
+        <v>-1.1939</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5836</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0583</v>
+        <v>-1.2027</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.0296</v>
+        <v>0.4622</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4811</v>
+        <v>1.0736</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5486</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4957</v>
+        <v>-1.6561</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1026</v>
+        <v>-1.0648</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6069</v>
+        <v>-0.5913</v>
       </c>
       <c r="P8" t="n">
         <v>0.5558999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1117</v>
+        <v>-0.1853</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6676</v>
+        <v>0.7411</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5409</v>
+        <v>-0.5779</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1131</v>
+        <v>-0.0892</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4278</v>
+        <v>-0.4887</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3144</v>
+        <v>0.0005</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3144</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. SANCHEZ SANCHEZ</t>
+          <t>J. VARO BARBANCHO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6077</v>
+        <v>-1.2687</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1061</v>
+        <v>-1.8215</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5016</v>
+        <v>0.5528</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1939</v>
+        <v>-1.5253</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008699999999999999</v>
+        <v>-1.5836</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2027</v>
+        <v>0.0583</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4622</v>
+        <v>-1.0296</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0736</v>
+        <v>-0.4811</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.5486</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6561</v>
+        <v>-0.4957</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0648</v>
+        <v>-1.1026</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5913</v>
+        <v>0.6069</v>
       </c>
       <c r="P9" t="n">
         <v>0.5558999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1853</v>
+        <v>-1.1117</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7411</v>
+        <v>1.6676</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9702</v>
+        <v>-0.6137</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.383</v>
+        <v>-0.309</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.3047</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0005</v>
+        <v>0.3144</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0005</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0852</v>
+        <v>-4.1601</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8232</v>
+        <v>-1.6274</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2619</v>
+        <v>-2.5328</v>
       </c>
       <c r="G10" t="n">
         <v>-2.1538</v>
@@ -1234,13 +1234,13 @@
         <v>1.297</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2104</v>
+        <v>-0.2854</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6019</v>
+        <v>-0.406</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3914</v>
+        <v>0.1206</v>
       </c>
       <c r="V10" t="n">
         <v>-2.8327</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0272</v>
+        <v>-4.7083</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7709</v>
+        <v>-2.575</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2563</v>
+        <v>-2.1332</v>
       </c>
       <c r="G11" t="n">
         <v>-3.7622</v>
@@ -1312,13 +1312,13 @@
         <v>0.3706</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3768</v>
+        <v>-0.0578</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3283</v>
+        <v>-0.1324</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0485</v>
+        <v>0.0746</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2589</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.903</v>
+        <v>-7.9031</v>
       </c>
       <c r="E12" t="n">
-        <v>4.9562</v>
+        <v>4.9561</v>
       </c>
       <c r="F12" t="n">
-        <v>-12.859</v>
+        <v>-12.8589</v>
       </c>
       <c r="G12" t="n">
         <v>-1.073699999999999</v>
@@ -1390,13 +1390,13 @@
         <v>12.0437</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2001</v>
+        <v>-1.2</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5844</v>
+        <v>-0.5842999999999998</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6158000000000001</v>
+        <v>-0.6156</v>
       </c>
       <c r="V12" t="n">
         <v>-3.7766</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B. CATALDO</t>
+          <t>M. MALICK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.7832</v>
+        <v>4.9645</v>
       </c>
       <c r="E13" t="n">
-        <v>6.3184</v>
+        <v>5.8724</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5352</v>
+        <v>-0.9078000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>4.3479</v>
+        <v>0.3354</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1313</v>
+        <v>-1.64</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2166</v>
+        <v>1.9754</v>
       </c>
       <c r="J13" t="n">
-        <v>4.8901</v>
+        <v>2.4491</v>
       </c>
       <c r="K13" t="n">
-        <v>4.0192</v>
+        <v>0.3127</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8709</v>
+        <v>2.1364</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5421</v>
+        <v>-2.1137</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8878</v>
+        <v>-1.9527</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3457</v>
+        <v>-0.161</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7411</v>
+        <v>2.594</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6676</v>
+        <v>2.594</v>
       </c>
       <c r="S13" t="n">
-        <v>2.268</v>
+        <v>0.1474</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4114</v>
+        <v>0.2767</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8565</v>
+        <v>-0.1294</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.5738</v>
+        <v>1.8877</v>
       </c>
       <c r="W13" t="n">
-        <v>0.9433</v>
+        <v>3.1466</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.5172</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. MALICK</t>
+          <t>B. CATALDO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.5029</v>
+        <v>4.312</v>
       </c>
       <c r="E14" t="n">
-        <v>6.4599</v>
+        <v>5.2412</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9571</v>
+        <v>-0.9291</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3354</v>
+        <v>4.3479</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.64</v>
+        <v>3.1313</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9754</v>
+        <v>1.2166</v>
       </c>
       <c r="J14" t="n">
-        <v>2.4491</v>
+        <v>4.8901</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3127</v>
+        <v>4.0192</v>
       </c>
       <c r="L14" t="n">
-        <v>2.1364</v>
+        <v>0.8709</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.1137</v>
+        <v>-0.5421</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.9527</v>
+        <v>-0.8878</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.161</v>
+        <v>0.3457</v>
       </c>
       <c r="P14" t="n">
-        <v>2.594</v>
+        <v>0.7411</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R14" t="n">
-        <v>2.594</v>
+        <v>1.6676</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6857</v>
+        <v>0.7968</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8643</v>
+        <v>0.3342</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1786</v>
+        <v>0.4626</v>
       </c>
       <c r="V14" t="n">
-        <v>1.8877</v>
+        <v>-1.5738</v>
       </c>
       <c r="W14" t="n">
-        <v>3.1466</v>
+        <v>0.9433</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2589</v>
+        <v>-2.5172</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. NDIAYE</t>
+          <t>J. FERNANDEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0567</v>
+        <v>1.277</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6339</v>
+        <v>1.4418</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5771</v>
+        <v>-0.1649</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6737</v>
+        <v>1.2056</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0342</v>
+        <v>-1.1275</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7079</v>
+        <v>2.3331</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6114</v>
+        <v>3.2815</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5285</v>
+        <v>0.6569</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0829</v>
+        <v>2.6246</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.2851</v>
+        <v>-2.0759</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4943</v>
+        <v>-1.7844</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-0.2915</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7411</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.8529</v>
+        <v>-4.6322</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1117</v>
+        <v>2.594</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2127</v>
+        <v>-0.4076</v>
       </c>
       <c r="T15" t="n">
-        <v>1.302</v>
+        <v>-0.3541</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0893</v>
+        <v>-0.0535</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2589</v>
+        <v>2.5172</v>
       </c>
       <c r="W15" t="n">
-        <v>1.5733</v>
+        <v>3.1466</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3144</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ HERNANDEZ</t>
+          <t>T. GARRETT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7392</v>
+        <v>1.0441</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7563</v>
+        <v>0.9811</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0171</v>
+        <v>0.0631</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2056</v>
+        <v>2.6054</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.1275</v>
+        <v>0.2629</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3331</v>
+        <v>2.3425</v>
       </c>
       <c r="J16" t="n">
-        <v>3.2815</v>
+        <v>3.6229</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6569</v>
+        <v>1.5802</v>
       </c>
       <c r="L16" t="n">
-        <v>2.6246</v>
+        <v>2.0428</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.0759</v>
+        <v>-1.0175</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.7844</v>
+        <v>-1.3173</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2915</v>
+        <v>0.2997</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.0382</v>
+        <v>-1.297</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.6322</v>
+        <v>-2.7793</v>
       </c>
       <c r="R16" t="n">
-        <v>2.594</v>
+        <v>1.4823</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9453</v>
+        <v>-0.2643</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0396</v>
+        <v>0.1374</v>
       </c>
       <c r="U16" t="n">
-        <v>0.09420000000000001</v>
+        <v>-0.4017</v>
       </c>
       <c r="V16" t="n">
-        <v>2.5172</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>3.1466</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. GARRETT</t>
+          <t>J. FERNÁNDEZ HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6267</v>
+        <v>0.3221</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7852</v>
+        <v>0.3221</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1585</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6054</v>
+        <v>0.3221</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2629</v>
+        <v>0.3221</v>
       </c>
       <c r="I17" t="n">
-        <v>2.3425</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6229</v>
+        <v>0.3221</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5802</v>
+        <v>0.3221</v>
       </c>
       <c r="L17" t="n">
-        <v>2.0428</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0175</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3173</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2997</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.297</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.7793</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4823</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6817</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0584</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6233</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. FERNÁNDEZ HERNÁNDEZ</t>
+          <t>F. NDIAYE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3221</v>
+        <v>0.2979</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3221</v>
+        <v>1.8504</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-1.5525</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3221</v>
+        <v>-0.6737</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3221</v>
+        <v>0.0342</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-0.7079</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3221</v>
+        <v>1.6114</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3221</v>
+        <v>1.5285</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.0829</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-2.2851</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-1.4943</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.1117</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.4539</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.5733</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0913</v>
+        <v>-0.2827</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2888</v>
+        <v>0.3967</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8025</v>
+        <v>-0.6794</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2083</v>
@@ -1936,13 +1936,13 @@
         <v>1.8529</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8655</v>
+        <v>-0.0569</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9849</v>
+        <v>-0.2994</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1194</v>
+        <v>0.2425</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9439</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4111</v>
+        <v>-0.6019</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0839</v>
+        <v>0.6714</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.495</v>
+        <v>-1.2734</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6564</v>
@@ -2014,13 +2014,13 @@
         <v>0.9264</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0523</v>
+        <v>-0.2431</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5471</v>
+        <v>0.0404</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5051</v>
+        <v>-0.2835</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6289</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6254</v>
+        <v>-3.4301</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.2118</v>
+        <v>-3.918</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5864</v>
+        <v>0.4879</v>
       </c>
       <c r="G21" t="n">
         <v>-6.2044</v>
@@ -2092,13 +2092,13 @@
         <v>1.6676</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5785</v>
+        <v>0.7738</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.332</v>
+        <v>-0.0382</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9105</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>1.2594</v>
@@ -2125,7 +2125,7 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>7.903000000000001</v>
+        <v>7.902900000000001</v>
       </c>
       <c r="E22" t="n">
         <v>12.8591</v>
@@ -2134,7 +2134,7 @@
         <v>-4.9561</v>
       </c>
       <c r="G22" t="n">
-        <v>1.073600000000001</v>
+        <v>1.073599999999999</v>
       </c>
       <c r="H22" t="n">
         <v>-2.1908</v>
@@ -2170,10 +2170,10 @@
         <v>13.8965</v>
       </c>
       <c r="S22" t="n">
-        <v>1.2001</v>
+        <v>1.2</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6156999999999999</v>
+        <v>0.6155999999999999</v>
       </c>
       <c r="U22" t="n">
         <v>0.5843000000000002</v>
@@ -2185,7 +2185,7 @@
         <v>10.3831</v>
       </c>
       <c r="X22" t="n">
-        <v>-6.606599999999999</v>
+        <v>-6.6066</v>
       </c>
     </row>
   </sheetData>
